--- a/research.xlsx
+++ b/research.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darowiin\Desktop\labs\ParallelProgramming\lab_3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Parallel__Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068ED2A1-D025-42E6-889E-5D41B495E278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EC007C-B43B-402A-B707-9A0FA3E4A9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D10AC719-3E9B-4D1A-9DB2-34D703C4A05A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D10AC719-3E9B-4D1A-9DB2-34D703C4A05A}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,29 +27,29 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Size</t>
+    <t>OpenMP (4)</t>
   </si>
   <si>
-    <t>Time(Without parallel)</t>
+    <t>OpenMP (12)</t>
   </si>
   <si>
-    <t>MPI(4)</t>
+    <t>MPI (4)</t>
   </si>
   <si>
-    <t>MPI(12)</t>
+    <t>MPI (12)</t>
   </si>
   <si>
-    <t>OpenMP(4)</t>
+    <t>Размер</t>
   </si>
   <si>
-    <t>OpenMP(12)</t>
+    <t>Последоват. запуск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +64,15 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -86,9 +95,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -266,34 +281,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.08267E-2</c:v>
+                  <c:v>1.0699999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.113564</c:v>
+                  <c:v>0.1115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.30675599999999997</c:v>
+                  <c:v>0.3049</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.67624700000000004</c:v>
+                  <c:v>0.67510000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3356699999999999</c:v>
+                  <c:v>1.3342000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.3715000000000002</c:v>
+                  <c:v>2.3696000000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.7705099999999998</c:v>
+                  <c:v>3.7688999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.6100599999999998</c:v>
+                  <c:v>5.6113</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.1979100000000003</c:v>
+                  <c:v>8.1982999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.830299999999999</c:v>
+                  <c:v>10.832599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -369,34 +384,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>3.4822E-3</c:v>
+                  <c:v>3.47E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9153199999999999E-2</c:v>
+                  <c:v>1.8919999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.5697700000000003E-2</c:v>
+                  <c:v>5.5210000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.137409</c:v>
+                  <c:v>0.13682</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.26932699999999998</c:v>
+                  <c:v>0.26890999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.44607599999999997</c:v>
+                  <c:v>0.44512000000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.73356699999999997</c:v>
+                  <c:v>0.73277999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0708</c:v>
+                  <c:v>1.0701000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5233399999999999</c:v>
+                  <c:v>1.5226</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.0294400000000001</c:v>
+                  <c:v>2.0287000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -472,34 +487,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.8295E-3</c:v>
+                  <c:v>2.81E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4138100000000001E-2</c:v>
+                  <c:v>1.4030000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7283999999999998E-2</c:v>
+                  <c:v>3.6979999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.3662500000000001E-2</c:v>
+                  <c:v>8.3119999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.15757099999999999</c:v>
+                  <c:v>0.15701000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.26514900000000002</c:v>
+                  <c:v>0.26479000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.41586000000000001</c:v>
+                  <c:v>0.41524</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.62166999999999994</c:v>
+                  <c:v>0.62102999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.90502700000000003</c:v>
+                  <c:v>0.90430999999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.2243599999999999</c:v>
+                  <c:v>1.2234100000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -577,34 +592,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.3109E-3</c:v>
+                  <c:v>1.2899999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0607699999999999E-2</c:v>
+                  <c:v>1.0410000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.13487E-2</c:v>
+                  <c:v>3.1210000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.9374299999999995E-2</c:v>
+                  <c:v>7.9049999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.143373</c:v>
+                  <c:v>0.14362</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.233429</c:v>
+                  <c:v>0.23313999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37764700000000001</c:v>
+                  <c:v>0.37712000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.58184999999999998</c:v>
+                  <c:v>0.58121999999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83974000000000004</c:v>
+                  <c:v>0.83918000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1348800000000001</c:v>
+                  <c:v>1.1342300000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -682,34 +697,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.4270999999999999E-3</c:v>
+                  <c:v>1.4499999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.8730000000000007E-3</c:v>
+                  <c:v>8.9099999999999995E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4579400000000001E-2</c:v>
+                  <c:v>2.453E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.6154199999999999E-2</c:v>
+                  <c:v>4.607E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.6519700000000005E-2</c:v>
+                  <c:v>8.6480000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.141874</c:v>
+                  <c:v>0.14182</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.226322</c:v>
+                  <c:v>0.22645000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.34161799999999998</c:v>
+                  <c:v>0.34156999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.49759399999999998</c:v>
+                  <c:v>0.49732999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.66353399999999996</c:v>
+                  <c:v>0.66325000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1839,224 +1854,224 @@
     <col min="3" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>100</v>
       </c>
-      <c r="B2">
-        <v>1.08267E-2</v>
-      </c>
-      <c r="C2">
-        <v>3.4822E-3</v>
-      </c>
-      <c r="D2">
-        <v>2.8295E-3</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1.3109E-3</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1.4270999999999999E-3</v>
+      <c r="B2" s="3">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>3.47E-3</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.81E-3</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1.2899999999999999E-3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.4499999999999999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>200</v>
       </c>
-      <c r="B3">
-        <v>0.113564</v>
-      </c>
-      <c r="C3">
-        <v>1.9153199999999999E-2</v>
-      </c>
-      <c r="D3">
-        <v>1.4138100000000001E-2</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.0607699999999999E-2</v>
-      </c>
-      <c r="F3" s="1">
-        <v>8.8730000000000007E-3</v>
+      <c r="B3" s="3">
+        <v>0.1115</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.8919999999999999E-2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.4030000000000001E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.0410000000000001E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8.9099999999999995E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>300</v>
       </c>
-      <c r="B4">
-        <v>0.30675599999999997</v>
-      </c>
-      <c r="C4">
-        <v>5.5697700000000003E-2</v>
-      </c>
-      <c r="D4">
-        <v>3.7283999999999998E-2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3.13487E-2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2.4579400000000001E-2</v>
+      <c r="B4" s="3">
+        <v>0.3049</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5.5210000000000002E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.6979999999999999E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.1210000000000002E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.453E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>400</v>
       </c>
-      <c r="B5">
-        <v>0.67624700000000004</v>
-      </c>
-      <c r="C5">
-        <v>0.137409</v>
-      </c>
-      <c r="D5">
-        <v>8.3662500000000001E-2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>7.9374299999999995E-2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4.6154199999999999E-2</v>
+      <c r="B5" s="3">
+        <v>0.67510000000000003</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.13682</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.3119999999999999E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>7.9049999999999995E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4.607E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>500</v>
       </c>
-      <c r="B6">
-        <v>1.3356699999999999</v>
-      </c>
-      <c r="C6">
-        <v>0.26932699999999998</v>
-      </c>
-      <c r="D6">
-        <v>0.15757099999999999</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.143373</v>
-      </c>
-      <c r="F6" s="1">
-        <v>8.6519700000000005E-2</v>
+      <c r="B6" s="3">
+        <v>1.3342000000000001</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.26890999999999998</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.15701000000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.14362</v>
+      </c>
+      <c r="F6" s="3">
+        <v>8.6480000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>600</v>
       </c>
-      <c r="B7">
-        <v>2.3715000000000002</v>
-      </c>
-      <c r="C7">
-        <v>0.44607599999999997</v>
-      </c>
-      <c r="D7">
-        <v>0.26514900000000002</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.233429</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0.141874</v>
+      <c r="B7" s="3">
+        <v>2.3696000000000002</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.44512000000000002</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.26479000000000003</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.23313999999999999</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.14182</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>700</v>
       </c>
-      <c r="B8">
-        <v>3.7705099999999998</v>
-      </c>
-      <c r="C8">
-        <v>0.73356699999999997</v>
-      </c>
-      <c r="D8">
-        <v>0.41586000000000001</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.37764700000000001</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.226322</v>
+      <c r="B8" s="3">
+        <v>3.7688999999999999</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.73277999999999999</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.41524</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.37712000000000001</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.22645000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>800</v>
       </c>
-      <c r="B9">
-        <v>5.6100599999999998</v>
-      </c>
-      <c r="C9">
-        <v>1.0708</v>
-      </c>
-      <c r="D9">
-        <v>0.62166999999999994</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.58184999999999998</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.34161799999999998</v>
+      <c r="B9" s="3">
+        <v>5.6113</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.0701000000000001</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.62102999999999997</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.58121999999999996</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.34156999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>900</v>
       </c>
-      <c r="B10">
-        <v>8.1979100000000003</v>
-      </c>
-      <c r="C10">
-        <v>1.5233399999999999</v>
-      </c>
-      <c r="D10">
-        <v>0.90502700000000003</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.83974000000000004</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.49759399999999998</v>
+      <c r="B10" s="3">
+        <v>8.1982999999999997</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.5226</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.90430999999999995</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.83918000000000004</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.49732999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>1000</v>
       </c>
-      <c r="B11">
-        <v>10.830299999999999</v>
-      </c>
-      <c r="C11">
-        <v>2.0294400000000001</v>
-      </c>
-      <c r="D11">
-        <v>1.2243599999999999</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1.1348800000000001</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.66353399999999996</v>
+      <c r="B11" s="3">
+        <v>10.832599999999999</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.0287000000000002</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.2234100000000001</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.1342300000000001</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.66325000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
